--- a/data/lossofsale_sg_kannur.xlsx
+++ b/data/lossofsale_sg_kannur.xlsx
@@ -2722,6 +2722,483 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="65">
+        <v>49</v>
+      </c>
+      <c t="inlineStr" r="B51">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C51">
+        <is>
+          <t xml:space="preserve">SHAFNAS</t>
+        </is>
+      </c>
+      <c r="D51" s="65">
+        <v>8792528247</v>
+      </c>
+      <c t="inlineStr" r="E51">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F51">
+        <is>
+          <t xml:space="preserve">ASWANTH. K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G51">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H51">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I51">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J51">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K51">
+        <is>
+          <t xml:space="preserve">LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="65">
+        <v>50</v>
+      </c>
+      <c t="inlineStr" r="B52">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C52">
+        <is>
+          <t xml:space="preserve">SOURAG</t>
+        </is>
+      </c>
+      <c r="D52" s="65">
+        <v>9633176056</v>
+      </c>
+      <c t="inlineStr" r="E52">
+        <is>
+          <t xml:space="preserve">25-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F52">
+        <is>
+          <t xml:space="preserve">FARIZ V A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G52">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H52">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I52">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J52">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K52">
+        <is>
+          <t xml:space="preserve">LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="65">
+        <v>51</v>
+      </c>
+      <c t="inlineStr" r="B53">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C53">
+        <is>
+          <t xml:space="preserve">MIHAD</t>
+        </is>
+      </c>
+      <c r="D53" s="65">
+        <v>6282504474</v>
+      </c>
+      <c t="inlineStr" r="E53">
+        <is>
+          <t xml:space="preserve">02-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F53">
+        <is>
+          <t xml:space="preserve">SHIDHIN A V</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G53">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H53">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I53">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J53">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K53">
+        <is>
+          <t xml:space="preserve">LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="65">
+        <v>52</v>
+      </c>
+      <c t="inlineStr" r="B54">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C54">
+        <is>
+          <t xml:space="preserve">AJMAL</t>
+        </is>
+      </c>
+      <c r="D54" s="65">
+        <v>7034000406</v>
+      </c>
+      <c t="inlineStr" r="E54">
+        <is>
+          <t xml:space="preserve">30-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F54">
+        <is>
+          <t xml:space="preserve">SHIDHIN A V</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G54">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H54">
+        <is>
+          <t xml:space="preserve">PRICING</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I54">
+        <is>
+          <t xml:space="preserve">RENT TO HIGH</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J54">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K54">
+        <is>
+          <t xml:space="preserve">LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="65">
+        <v>53</v>
+      </c>
+      <c t="inlineStr" r="B55">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C55">
+        <is>
+          <t xml:space="preserve">NIVED</t>
+        </is>
+      </c>
+      <c r="D55" s="65">
+        <v>9847020918</v>
+      </c>
+      <c t="inlineStr" r="E55">
+        <is>
+          <t xml:space="preserve">24-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F55">
+        <is>
+          <t xml:space="preserve">ASWANTH. K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G55">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H55">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I55">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J55">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K55">
+        <is>
+          <t xml:space="preserve">LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="65">
+        <v>54</v>
+      </c>
+      <c t="inlineStr" r="B56">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C56">
+        <is>
+          <t xml:space="preserve">ASWANTH</t>
+        </is>
+      </c>
+      <c r="D56" s="65">
+        <v>8848826239</v>
+      </c>
+      <c t="inlineStr" r="E56">
+        <is>
+          <t xml:space="preserve">02-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F56">
+        <is>
+          <t xml:space="preserve">ASWANTH. K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G56">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H56">
+        <is>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I56">
+        <is>
+          <t xml:space="preserve">SIZE TOO SMALL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J56">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K56">
+        <is>
+          <t xml:space="preserve">LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="65">
+        <v>55</v>
+      </c>
+      <c t="inlineStr" r="B57">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C57">
+        <is>
+          <t xml:space="preserve">ATHUL</t>
+        </is>
+      </c>
+      <c r="D57" s="65">
+        <v>9745577506</v>
+      </c>
+      <c t="inlineStr" r="E57">
+        <is>
+          <t xml:space="preserve">11-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F57">
+        <is>
+          <t xml:space="preserve">Thejus R</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G57">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H57">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I57">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J57">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K57">
+        <is>
+          <t xml:space="preserve">WILL COME</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="65">
+        <v>56</v>
+      </c>
+      <c t="inlineStr" r="B58">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C58">
+        <is>
+          <t xml:space="preserve">adwin</t>
+        </is>
+      </c>
+      <c r="D58" s="65">
+        <v>9446330750</v>
+      </c>
+      <c t="inlineStr" r="E58">
+        <is>
+          <t xml:space="preserve">12-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F58">
+        <is>
+          <t xml:space="preserve">ASWANTH. K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G58">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H58">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I58">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J58">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K58">
+        <is>
+          <t xml:space="preserve">loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="65">
+        <v>57</v>
+      </c>
+      <c t="inlineStr" r="B59">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C59">
+        <is>
+          <t xml:space="preserve">SINAN</t>
+        </is>
+      </c>
+      <c r="D59" s="65">
+        <v>9037030088</v>
+      </c>
+      <c t="inlineStr" r="E59">
+        <is>
+          <t xml:space="preserve">04-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F59">
+        <is>
+          <t xml:space="preserve">JISHNU RAJ K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G59">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H59">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I59">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J59">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K59">
+        <is>
+          <t xml:space="preserve">LOSS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
